--- a/nr-update-frcore-2.2.0/ig/StructureDefinition-as-practitionerrole.xlsx
+++ b/nr-update-frcore-2.2.0/ig/StructureDefinition-as-practitionerrole.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-snapshot-1</t>
+    <t>1.2.0-snapshot-2</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T11:49:33+00:00</t>
+    <t>2026-06-18T12:07:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -661,7 +661,7 @@
     <t>as-ext-practitionerrole-contracted</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-practitionerrole-contracted|1.2.0-snapshot-1}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-practitionerrole-contracted|1.2.0-snapshot-2}
 </t>
   </si>
   <si>
@@ -677,7 +677,7 @@
     <t>as-ext-practitionerrole-hascas</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-practitionerrole-hascas|1.2.0-snapshot-1}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-practitionerrole-hascas|1.2.0-snapshot-2}
 </t>
   </si>
   <si>
@@ -693,7 +693,7 @@
     <t>as-ext-practitionerrole-vitale-accepted</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-practitionerrole-vitale-accepted|1.2.0-snapshot-1}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-practitionerrole-vitale-accepted|1.2.0-snapshot-2}
 </t>
   </si>
   <si>
@@ -1127,7 +1127,7 @@
     <t>PractitionerRole.practitioner</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-practitioner|1.2.0-snapshot-1)
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-practitioner|1.2.0-snapshot-2)
 </t>
   </si>
   <si>
@@ -1143,7 +1143,7 @@
     <t>PractitionerRole.organization</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-organization|1.2.0-snapshot-1)
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-organization|1.2.0-snapshot-2)
 </t>
   </si>
   <si>
@@ -1534,7 +1534,7 @@
     <t>mailbox-mss</t>
   </si>
   <si>
-    <t xml:space="preserve">ContactPoint {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-mailbox-mss|1.2.0-snapshot-1}
+    <t xml:space="preserve">ContactPoint {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-mailbox-mss|1.2.0-snapshot-2}
 </t>
   </si>
   <si>
@@ -1619,7 +1619,7 @@
     <t>as-mailbox-mss-metadata</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-mailbox-mss-metadata|1.2.0-snapshot-1}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-mailbox-mss-metadata|1.2.0-snapshot-2}
 </t>
   </si>
   <si>

--- a/nr-update-frcore-2.2.0/ig/StructureDefinition-as-practitionerrole.xlsx
+++ b/nr-update-frcore-2.2.0/ig/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T12:07:50+00:00</t>
+    <t>2026-06-18T13:08:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-update-frcore-2.2.0/ig/StructureDefinition-as-practitionerrole.xlsx
+++ b/nr-update-frcore-2.2.0/ig/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T13:08:38+00:00</t>
+    <t>2026-06-18T13:31:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
